--- a/artfynd/A 1500-2022 artfynd.xlsx
+++ b/artfynd/A 1500-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1500-2022 artfynd.xlsx
+++ b/artfynd/A 1500-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114567061</v>
+        <v>114567542</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Munga-Horndal, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582136</v>
+        <v>582125</v>
       </c>
       <c r="R2" t="n">
-        <v>6662483</v>
+        <v>6662477</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -770,22 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114567542</v>
+        <v>114757500</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,20 +814,24 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Munga-Horndal, Vstm</t>
+          <t>Hoberget, 300 m NV om (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582125</v>
+        <v>582122</v>
       </c>
       <c r="R3" t="n">
-        <v>6662477</v>
+        <v>6662677</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +854,11 @@
       <c r="W3" t="inlineStr">
         <is>
           <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>U-Sal-0822</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -876,15 +884,218 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114567061</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>582136</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6662483</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mårten Nilsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114567544</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Munga-Horndal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>581835</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6662773</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Johan Kjetselberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1500-2022 artfynd.xlsx
+++ b/artfynd/A 1500-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567542</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
           <t>Floraväkteri Sverige, Inventering längs blivande kraftledning Munga-Horndal</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114757500</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567061</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567544</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>